--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1521"/>
+  <dimension ref="A1:D1524"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -21678,6 +21678,48 @@
         <v>497.56</v>
       </c>
     </row>
+    <row r="1522" spans="1:4">
+      <c r="A1522" s="1">
+        <v>1520</v>
+      </c>
+      <c r="B1522" s="2">
+        <v>46082</v>
+      </c>
+      <c r="C1522">
+        <v>1</v>
+      </c>
+      <c r="D1522">
+        <v>497.56</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:4">
+      <c r="A1523" s="1">
+        <v>1521</v>
+      </c>
+      <c r="B1523" s="2">
+        <v>46083</v>
+      </c>
+      <c r="C1523">
+        <v>1</v>
+      </c>
+      <c r="D1523">
+        <v>497.56</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:4">
+      <c r="A1524" s="1">
+        <v>1522</v>
+      </c>
+      <c r="B1524" s="2">
+        <v>46084</v>
+      </c>
+      <c r="C1524">
+        <v>1</v>
+      </c>
+      <c r="D1524">
+        <v>502.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1524"/>
+  <dimension ref="A1:D1525"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -21720,6 +21720,20 @@
         <v>502.6</v>
       </c>
     </row>
+    <row r="1525" spans="1:4">
+      <c r="A1525" s="1">
+        <v>1523</v>
+      </c>
+      <c r="B1525" s="2">
+        <v>46085</v>
+      </c>
+      <c r="C1525">
+        <v>1</v>
+      </c>
+      <c r="D1525">
+        <v>498.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1525"/>
+  <dimension ref="A1:D1526"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -21734,6 +21734,20 @@
         <v>498.09</v>
       </c>
     </row>
+    <row r="1526" spans="1:4">
+      <c r="A1526" s="1">
+        <v>1524</v>
+      </c>
+      <c r="B1526" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C1526">
+        <v>1</v>
+      </c>
+      <c r="D1526">
+        <v>499.83</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1526"/>
+  <dimension ref="A1:D1527"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -21748,6 +21748,20 @@
         <v>499.83</v>
       </c>
     </row>
+    <row r="1527" spans="1:4">
+      <c r="A1527" s="1">
+        <v>1525</v>
+      </c>
+      <c r="B1527" s="2">
+        <v>46087</v>
+      </c>
+      <c r="C1527">
+        <v>1</v>
+      </c>
+      <c r="D1527">
+        <v>493.36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1527"/>
+  <dimension ref="A1:D1528"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -21762,6 +21762,20 @@
         <v>493.36</v>
       </c>
     </row>
+    <row r="1528" spans="1:4">
+      <c r="A1528" s="1">
+        <v>1526</v>
+      </c>
+      <c r="B1528" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C1528">
+        <v>1</v>
+      </c>
+      <c r="D1528">
+        <v>493.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1528"/>
+  <dimension ref="A1:D1531"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -21776,6 +21776,48 @@
         <v>493.85</v>
       </c>
     </row>
+    <row r="1529" spans="1:4">
+      <c r="A1529" s="1">
+        <v>1527</v>
+      </c>
+      <c r="B1529" s="2">
+        <v>46089</v>
+      </c>
+      <c r="C1529">
+        <v>1</v>
+      </c>
+      <c r="D1529">
+        <v>493.85</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:4">
+      <c r="A1530" s="1">
+        <v>1528</v>
+      </c>
+      <c r="B1530" s="2">
+        <v>46090</v>
+      </c>
+      <c r="C1530">
+        <v>1</v>
+      </c>
+      <c r="D1530">
+        <v>493.85</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:4">
+      <c r="A1531" s="1">
+        <v>1529</v>
+      </c>
+      <c r="B1531" s="2">
+        <v>46091</v>
+      </c>
+      <c r="C1531">
+        <v>1</v>
+      </c>
+      <c r="D1531">
+        <v>493.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1531"/>
+  <dimension ref="A1:D1532"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -21818,6 +21818,20 @@
         <v>493.85</v>
       </c>
     </row>
+    <row r="1532" spans="1:4">
+      <c r="A1532" s="1">
+        <v>1530</v>
+      </c>
+      <c r="B1532" s="2">
+        <v>46092</v>
+      </c>
+      <c r="C1532">
+        <v>1</v>
+      </c>
+      <c r="D1532">
+        <v>491.59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1532"/>
+  <dimension ref="A1:D1533"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -21832,6 +21832,20 @@
         <v>491.59</v>
       </c>
     </row>
+    <row r="1533" spans="1:4">
+      <c r="A1533" s="1">
+        <v>1531</v>
+      </c>
+      <c r="B1533" s="2">
+        <v>46093</v>
+      </c>
+      <c r="C1533">
+        <v>1</v>
+      </c>
+      <c r="D1533">
+        <v>489.39</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1533"/>
+  <dimension ref="A1:D1534"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -21846,6 +21846,20 @@
         <v>489.39</v>
       </c>
     </row>
+    <row r="1534" spans="1:4">
+      <c r="A1534" s="1">
+        <v>1532</v>
+      </c>
+      <c r="B1534" s="2">
+        <v>46094</v>
+      </c>
+      <c r="C1534">
+        <v>1</v>
+      </c>
+      <c r="D1534">
+        <v>491.68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1534"/>
+  <dimension ref="A1:D1535"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -21860,6 +21860,20 @@
         <v>491.68</v>
       </c>
     </row>
+    <row r="1535" spans="1:4">
+      <c r="A1535" s="1">
+        <v>1533</v>
+      </c>
+      <c r="B1535" s="2">
+        <v>46095</v>
+      </c>
+      <c r="C1535">
+        <v>1</v>
+      </c>
+      <c r="D1535">
+        <v>491.29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1535"/>
+  <dimension ref="A1:D1538"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -21874,6 +21874,48 @@
         <v>491.29</v>
       </c>
     </row>
+    <row r="1536" spans="1:4">
+      <c r="A1536" s="1">
+        <v>1534</v>
+      </c>
+      <c r="B1536" s="2">
+        <v>46096</v>
+      </c>
+      <c r="C1536">
+        <v>1</v>
+      </c>
+      <c r="D1536">
+        <v>491.29</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:4">
+      <c r="A1537" s="1">
+        <v>1535</v>
+      </c>
+      <c r="B1537" s="2">
+        <v>46097</v>
+      </c>
+      <c r="C1537">
+        <v>1</v>
+      </c>
+      <c r="D1537">
+        <v>491.29</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:4">
+      <c r="A1538" s="1">
+        <v>1536</v>
+      </c>
+      <c r="B1538" s="2">
+        <v>46098</v>
+      </c>
+      <c r="C1538">
+        <v>1</v>
+      </c>
+      <c r="D1538">
+        <v>486.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1538"/>
+  <dimension ref="A1:D1539"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -21916,6 +21916,20 @@
         <v>486.2</v>
       </c>
     </row>
+    <row r="1539" spans="1:4">
+      <c r="A1539" s="1">
+        <v>1537</v>
+      </c>
+      <c r="B1539" s="2">
+        <v>46099</v>
+      </c>
+      <c r="C1539">
+        <v>1</v>
+      </c>
+      <c r="D1539">
+        <v>479.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1539"/>
+  <dimension ref="A1:D1540"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -21930,6 +21930,20 @@
         <v>479.02</v>
       </c>
     </row>
+    <row r="1540" spans="1:4">
+      <c r="A1540" s="1">
+        <v>1538</v>
+      </c>
+      <c r="B1540" s="2">
+        <v>46100</v>
+      </c>
+      <c r="C1540">
+        <v>1</v>
+      </c>
+      <c r="D1540">
+        <v>482.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1540"/>
+  <dimension ref="A1:D1541"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -21944,6 +21944,20 @@
         <v>482.49</v>
       </c>
     </row>
+    <row r="1541" spans="1:4">
+      <c r="A1541" s="1">
+        <v>1539</v>
+      </c>
+      <c r="B1541" s="2">
+        <v>46101</v>
+      </c>
+      <c r="C1541">
+        <v>1</v>
+      </c>
+      <c r="D1541">
+        <v>482.32</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1541"/>
+  <dimension ref="A1:D1542"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -21958,6 +21958,20 @@
         <v>482.32</v>
       </c>
     </row>
+    <row r="1542" spans="1:4">
+      <c r="A1542" s="1">
+        <v>1540</v>
+      </c>
+      <c r="B1542" s="2">
+        <v>46102</v>
+      </c>
+      <c r="C1542">
+        <v>1</v>
+      </c>
+      <c r="D1542">
+        <v>482.33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1542"/>
+  <dimension ref="A1:D1545"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -21972,6 +21972,48 @@
         <v>482.33</v>
       </c>
     </row>
+    <row r="1543" spans="1:4">
+      <c r="A1543" s="1">
+        <v>1541</v>
+      </c>
+      <c r="B1543" s="2">
+        <v>46103</v>
+      </c>
+      <c r="C1543">
+        <v>1</v>
+      </c>
+      <c r="D1543">
+        <v>482.33</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:4">
+      <c r="A1544" s="1">
+        <v>1542</v>
+      </c>
+      <c r="B1544" s="2">
+        <v>46104</v>
+      </c>
+      <c r="C1544">
+        <v>1</v>
+      </c>
+      <c r="D1544">
+        <v>482.33</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:4">
+      <c r="A1545" s="1">
+        <v>1543</v>
+      </c>
+      <c r="B1545" s="2">
+        <v>46105</v>
+      </c>
+      <c r="C1545">
+        <v>1</v>
+      </c>
+      <c r="D1545">
+        <v>482.33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1545"/>
+  <dimension ref="A1:D1546"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22014,6 +22014,20 @@
         <v>482.33</v>
       </c>
     </row>
+    <row r="1546" spans="1:4">
+      <c r="A1546" s="1">
+        <v>1544</v>
+      </c>
+      <c r="B1546" s="2">
+        <v>46106</v>
+      </c>
+      <c r="C1546">
+        <v>1</v>
+      </c>
+      <c r="D1546">
+        <v>482.33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1546"/>
+  <dimension ref="A1:D1547"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22028,6 +22028,20 @@
         <v>482.33</v>
       </c>
     </row>
+    <row r="1547" spans="1:4">
+      <c r="A1547" s="1">
+        <v>1545</v>
+      </c>
+      <c r="B1547" s="2">
+        <v>46107</v>
+      </c>
+      <c r="C1547">
+        <v>1</v>
+      </c>
+      <c r="D1547">
+        <v>482.33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1547"/>
+  <dimension ref="A1:D1548"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22042,6 +22042,20 @@
         <v>482.33</v>
       </c>
     </row>
+    <row r="1548" spans="1:4">
+      <c r="A1548" s="1">
+        <v>1546</v>
+      </c>
+      <c r="B1548" s="2">
+        <v>46108</v>
+      </c>
+      <c r="C1548">
+        <v>1</v>
+      </c>
+      <c r="D1548">
+        <v>481.83</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1548"/>
+  <dimension ref="A1:D1549"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22056,6 +22056,20 @@
         <v>481.83</v>
       </c>
     </row>
+    <row r="1549" spans="1:4">
+      <c r="A1549" s="1">
+        <v>1547</v>
+      </c>
+      <c r="B1549" s="2">
+        <v>46109</v>
+      </c>
+      <c r="C1549">
+        <v>1</v>
+      </c>
+      <c r="D1549">
+        <v>482.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1549"/>
+  <dimension ref="A1:D1552"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22070,6 +22070,48 @@
         <v>482.53</v>
       </c>
     </row>
+    <row r="1550" spans="1:4">
+      <c r="A1550" s="1">
+        <v>1548</v>
+      </c>
+      <c r="B1550" s="2">
+        <v>46110</v>
+      </c>
+      <c r="C1550">
+        <v>1</v>
+      </c>
+      <c r="D1550">
+        <v>482.53</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:4">
+      <c r="A1551" s="1">
+        <v>1549</v>
+      </c>
+      <c r="B1551" s="2">
+        <v>46111</v>
+      </c>
+      <c r="C1551">
+        <v>1</v>
+      </c>
+      <c r="D1551">
+        <v>482.53</v>
+      </c>
+    </row>
+    <row r="1552" spans="1:4">
+      <c r="A1552" s="1">
+        <v>1550</v>
+      </c>
+      <c r="B1552" s="2">
+        <v>46112</v>
+      </c>
+      <c r="C1552">
+        <v>1</v>
+      </c>
+      <c r="D1552">
+        <v>481.54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1552"/>
+  <dimension ref="A1:D1553"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22112,6 +22112,20 @@
         <v>481.54</v>
       </c>
     </row>
+    <row r="1553" spans="1:4">
+      <c r="A1553" s="1">
+        <v>1551</v>
+      </c>
+      <c r="B1553" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C1553">
+        <v>1</v>
+      </c>
+      <c r="D1553">
+        <v>478.77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1553"/>
+  <dimension ref="A1:D1554"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22126,6 +22126,20 @@
         <v>478.77</v>
       </c>
     </row>
+    <row r="1554" spans="1:4">
+      <c r="A1554" s="1">
+        <v>1552</v>
+      </c>
+      <c r="B1554" s="2">
+        <v>46114</v>
+      </c>
+      <c r="C1554">
+        <v>1</v>
+      </c>
+      <c r="D1554">
+        <v>475.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1554"/>
+  <dimension ref="A1:D1555"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22140,6 +22140,20 @@
         <v>475.09</v>
       </c>
     </row>
+    <row r="1555" spans="1:4">
+      <c r="A1555" s="1">
+        <v>1553</v>
+      </c>
+      <c r="B1555" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C1555">
+        <v>1</v>
+      </c>
+      <c r="D1555">
+        <v>472.31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1555"/>
+  <dimension ref="A1:D1556"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22154,6 +22154,20 @@
         <v>472.31</v>
       </c>
     </row>
+    <row r="1556" spans="1:4">
+      <c r="A1556" s="1">
+        <v>1554</v>
+      </c>
+      <c r="B1556" s="2">
+        <v>46116</v>
+      </c>
+      <c r="C1556">
+        <v>1</v>
+      </c>
+      <c r="D1556">
+        <v>470.46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1556"/>
+  <dimension ref="A1:D1558"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22168,6 +22168,34 @@
         <v>470.46</v>
       </c>
     </row>
+    <row r="1557" spans="1:4">
+      <c r="A1557" s="1">
+        <v>1555</v>
+      </c>
+      <c r="B1557" s="2">
+        <v>46117</v>
+      </c>
+      <c r="C1557">
+        <v>1</v>
+      </c>
+      <c r="D1557">
+        <v>470.46</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:4">
+      <c r="A1558" s="1">
+        <v>1556</v>
+      </c>
+      <c r="B1558" s="2">
+        <v>46118</v>
+      </c>
+      <c r="C1558">
+        <v>1</v>
+      </c>
+      <c r="D1558">
+        <v>470.46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1558"/>
+  <dimension ref="A1:D1559"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22196,6 +22196,20 @@
         <v>470.46</v>
       </c>
     </row>
+    <row r="1559" spans="1:4">
+      <c r="A1559" s="1">
+        <v>1557</v>
+      </c>
+      <c r="B1559" s="2">
+        <v>46119</v>
+      </c>
+      <c r="C1559">
+        <v>1</v>
+      </c>
+      <c r="D1559">
+        <v>466.33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1559"/>
+  <dimension ref="A1:D1560"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22210,6 +22210,20 @@
         <v>466.33</v>
       </c>
     </row>
+    <row r="1560" spans="1:4">
+      <c r="A1560" s="1">
+        <v>1558</v>
+      </c>
+      <c r="B1560" s="2">
+        <v>46120</v>
+      </c>
+      <c r="C1560">
+        <v>1</v>
+      </c>
+      <c r="D1560">
+        <v>460.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1560"/>
+  <dimension ref="A1:D1561"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22224,6 +22224,20 @@
         <v>460.37</v>
       </c>
     </row>
+    <row r="1561" spans="1:4">
+      <c r="A1561" s="1">
+        <v>1559</v>
+      </c>
+      <c r="B1561" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C1561">
+        <v>1</v>
+      </c>
+      <c r="D1561">
+        <v>475.31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1561"/>
+  <dimension ref="A1:D1562"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22238,6 +22238,20 @@
         <v>475.31</v>
       </c>
     </row>
+    <row r="1562" spans="1:4">
+      <c r="A1562" s="1">
+        <v>1560</v>
+      </c>
+      <c r="B1562" s="2">
+        <v>46122</v>
+      </c>
+      <c r="C1562">
+        <v>1</v>
+      </c>
+      <c r="D1562">
+        <v>479.82</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1562"/>
+  <dimension ref="A1:D1563"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22252,6 +22252,20 @@
         <v>479.82</v>
       </c>
     </row>
+    <row r="1563" spans="1:4">
+      <c r="A1563" s="1">
+        <v>1561</v>
+      </c>
+      <c r="B1563" s="2">
+        <v>46123</v>
+      </c>
+      <c r="C1563">
+        <v>1</v>
+      </c>
+      <c r="D1563">
+        <v>473.13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1563"/>
+  <dimension ref="A1:D1565"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22266,6 +22266,34 @@
         <v>473.13</v>
       </c>
     </row>
+    <row r="1564" spans="1:4">
+      <c r="A1564" s="1">
+        <v>1562</v>
+      </c>
+      <c r="B1564" s="2">
+        <v>46124</v>
+      </c>
+      <c r="C1564">
+        <v>1</v>
+      </c>
+      <c r="D1564">
+        <v>473.13</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:4">
+      <c r="A1565" s="1">
+        <v>1563</v>
+      </c>
+      <c r="B1565" s="2">
+        <v>46125</v>
+      </c>
+      <c r="C1565">
+        <v>1</v>
+      </c>
+      <c r="D1565">
+        <v>473.13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1565"/>
+  <dimension ref="A1:D1566"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22294,6 +22294,20 @@
         <v>473.13</v>
       </c>
     </row>
+    <row r="1566" spans="1:4">
+      <c r="A1566" s="1">
+        <v>1564</v>
+      </c>
+      <c r="B1566" s="2">
+        <v>46126</v>
+      </c>
+      <c r="C1566">
+        <v>1</v>
+      </c>
+      <c r="D1566">
+        <v>474.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1566"/>
+  <dimension ref="A1:D1567"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22308,6 +22308,20 @@
         <v>474.9</v>
       </c>
     </row>
+    <row r="1567" spans="1:4">
+      <c r="A1567" s="1">
+        <v>1565</v>
+      </c>
+      <c r="B1567" s="2">
+        <v>46127</v>
+      </c>
+      <c r="C1567">
+        <v>1</v>
+      </c>
+      <c r="D1567">
+        <v>476.97</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1567"/>
+  <dimension ref="A1:D1568"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22322,6 +22322,20 @@
         <v>476.97</v>
       </c>
     </row>
+    <row r="1568" spans="1:4">
+      <c r="A1568" s="1">
+        <v>1566</v>
+      </c>
+      <c r="B1568" s="2">
+        <v>46128</v>
+      </c>
+      <c r="C1568">
+        <v>1</v>
+      </c>
+      <c r="D1568">
+        <v>474.08</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1568"/>
+  <dimension ref="A1:D1569"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22336,6 +22336,20 @@
         <v>474.08</v>
       </c>
     </row>
+    <row r="1569" spans="1:4">
+      <c r="A1569" s="1">
+        <v>1567</v>
+      </c>
+      <c r="B1569" s="2">
+        <v>46129</v>
+      </c>
+      <c r="C1569">
+        <v>1</v>
+      </c>
+      <c r="D1569">
+        <v>471.46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1569"/>
+  <dimension ref="A1:D1570"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22350,6 +22350,20 @@
         <v>471.46</v>
       </c>
     </row>
+    <row r="1570" spans="1:4">
+      <c r="A1570" s="1">
+        <v>1568</v>
+      </c>
+      <c r="B1570" s="2">
+        <v>46130</v>
+      </c>
+      <c r="C1570">
+        <v>1</v>
+      </c>
+      <c r="D1570">
+        <v>469.52</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1570"/>
+  <dimension ref="A1:D1572"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22364,6 +22364,34 @@
         <v>469.52</v>
       </c>
     </row>
+    <row r="1571" spans="1:4">
+      <c r="A1571" s="1">
+        <v>1569</v>
+      </c>
+      <c r="B1571" s="2">
+        <v>46131</v>
+      </c>
+      <c r="C1571">
+        <v>1</v>
+      </c>
+      <c r="D1571">
+        <v>469.52</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:4">
+      <c r="A1572" s="1">
+        <v>1570</v>
+      </c>
+      <c r="B1572" s="2">
+        <v>46132</v>
+      </c>
+      <c r="C1572">
+        <v>1</v>
+      </c>
+      <c r="D1572">
+        <v>469.52</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1572"/>
+  <dimension ref="A1:D1573"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22392,6 +22392,20 @@
         <v>469.52</v>
       </c>
     </row>
+    <row r="1573" spans="1:4">
+      <c r="A1573" s="1">
+        <v>1571</v>
+      </c>
+      <c r="B1573" s="2">
+        <v>46133</v>
+      </c>
+      <c r="C1573">
+        <v>1</v>
+      </c>
+      <c r="D1573">
+        <v>469.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1573"/>
+  <dimension ref="A1:D1574"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22406,6 +22406,20 @@
         <v>469.49</v>
       </c>
     </row>
+    <row r="1574" spans="1:4">
+      <c r="A1574" s="1">
+        <v>1572</v>
+      </c>
+      <c r="B1574" s="2">
+        <v>46134</v>
+      </c>
+      <c r="C1574">
+        <v>1</v>
+      </c>
+      <c r="D1574">
+        <v>464.73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1574"/>
+  <dimension ref="A1:D1575"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22420,6 +22420,20 @@
         <v>464.73</v>
       </c>
     </row>
+    <row r="1575" spans="1:4">
+      <c r="A1575" s="1">
+        <v>1573</v>
+      </c>
+      <c r="B1575" s="2">
+        <v>46135</v>
+      </c>
+      <c r="C1575">
+        <v>1</v>
+      </c>
+      <c r="D1575">
+        <v>461.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1575"/>
+  <dimension ref="A1:D1576"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22434,6 +22434,20 @@
         <v>461.37</v>
       </c>
     </row>
+    <row r="1576" spans="1:4">
+      <c r="A1576" s="1">
+        <v>1574</v>
+      </c>
+      <c r="B1576" s="2">
+        <v>46136</v>
+      </c>
+      <c r="C1576">
+        <v>1</v>
+      </c>
+      <c r="D1576">
+        <v>462.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1576"/>
+  <dimension ref="A1:D1577"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22448,6 +22448,20 @@
         <v>462.87</v>
       </c>
     </row>
+    <row r="1577" spans="1:4">
+      <c r="A1577" s="1">
+        <v>1575</v>
+      </c>
+      <c r="B1577" s="2">
+        <v>46137</v>
+      </c>
+      <c r="C1577">
+        <v>1</v>
+      </c>
+      <c r="D1577">
+        <v>464.86</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1577"/>
+  <dimension ref="A1:D1580"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22462,6 +22462,48 @@
         <v>464.86</v>
       </c>
     </row>
+    <row r="1578" spans="1:4">
+      <c r="A1578" s="1">
+        <v>1576</v>
+      </c>
+      <c r="B1578" s="2">
+        <v>46138</v>
+      </c>
+      <c r="C1578">
+        <v>1</v>
+      </c>
+      <c r="D1578">
+        <v>464.86</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:4">
+      <c r="A1579" s="1">
+        <v>1577</v>
+      </c>
+      <c r="B1579" s="2">
+        <v>46139</v>
+      </c>
+      <c r="C1579">
+        <v>1</v>
+      </c>
+      <c r="D1579">
+        <v>464.86</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:4">
+      <c r="A1580" s="1">
+        <v>1578</v>
+      </c>
+      <c r="B1580" s="2">
+        <v>46140</v>
+      </c>
+      <c r="C1580">
+        <v>1</v>
+      </c>
+      <c r="D1580">
+        <v>460.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1580"/>
+  <dimension ref="A1:D1581"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22504,6 +22504,20 @@
         <v>460.8</v>
       </c>
     </row>
+    <row r="1581" spans="1:4">
+      <c r="A1581" s="1">
+        <v>1579</v>
+      </c>
+      <c r="B1581" s="2">
+        <v>46141</v>
+      </c>
+      <c r="C1581">
+        <v>1</v>
+      </c>
+      <c r="D1581">
+        <v>457.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1581"/>
+  <dimension ref="A1:D1582"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22518,6 +22518,20 @@
         <v>457.21</v>
       </c>
     </row>
+    <row r="1582" spans="1:4">
+      <c r="A1582" s="1">
+        <v>1580</v>
+      </c>
+      <c r="B1582" s="2">
+        <v>46142</v>
+      </c>
+      <c r="C1582">
+        <v>1</v>
+      </c>
+      <c r="D1582">
+        <v>461.55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1582"/>
+  <dimension ref="A1:D1583"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22532,6 +22532,20 @@
         <v>461.55</v>
       </c>
     </row>
+    <row r="1583" spans="1:4">
+      <c r="A1583" s="1">
+        <v>1581</v>
+      </c>
+      <c r="B1583" s="2">
+        <v>46143</v>
+      </c>
+      <c r="C1583">
+        <v>1</v>
+      </c>
+      <c r="D1583">
+        <v>462.91</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1583"/>
+  <dimension ref="A1:D1585"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22546,6 +22546,34 @@
         <v>462.91</v>
       </c>
     </row>
+    <row r="1584" spans="1:4">
+      <c r="A1584" s="1">
+        <v>1582</v>
+      </c>
+      <c r="B1584" s="2">
+        <v>46144</v>
+      </c>
+      <c r="C1584">
+        <v>1</v>
+      </c>
+      <c r="D1584">
+        <v>462.91</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:4">
+      <c r="A1585" s="1">
+        <v>1583</v>
+      </c>
+      <c r="B1585" s="2">
+        <v>46145</v>
+      </c>
+      <c r="C1585">
+        <v>1</v>
+      </c>
+      <c r="D1585">
+        <v>462.91</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1585"/>
+  <dimension ref="A1:D1586"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22574,6 +22574,20 @@
         <v>462.91</v>
       </c>
     </row>
+    <row r="1586" spans="1:4">
+      <c r="A1586" s="1">
+        <v>1584</v>
+      </c>
+      <c r="B1586" s="2">
+        <v>46146</v>
+      </c>
+      <c r="C1586">
+        <v>1</v>
+      </c>
+      <c r="D1586">
+        <v>462.91</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1586"/>
+  <dimension ref="A1:D1587"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22588,6 +22588,20 @@
         <v>462.91</v>
       </c>
     </row>
+    <row r="1587" spans="1:4">
+      <c r="A1587" s="1">
+        <v>1585</v>
+      </c>
+      <c r="B1587" s="2">
+        <v>46147</v>
+      </c>
+      <c r="C1587">
+        <v>1</v>
+      </c>
+      <c r="D1587">
+        <v>464.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1587"/>
+  <dimension ref="A1:D1588"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22602,6 +22602,20 @@
         <v>464.53</v>
       </c>
     </row>
+    <row r="1588" spans="1:4">
+      <c r="A1588" s="1">
+        <v>1586</v>
+      </c>
+      <c r="B1588" s="2">
+        <v>46148</v>
+      </c>
+      <c r="C1588">
+        <v>1</v>
+      </c>
+      <c r="D1588">
+        <v>465.01</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1588"/>
+  <dimension ref="A1:D1589"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22616,6 +22616,20 @@
         <v>465.01</v>
       </c>
     </row>
+    <row r="1589" spans="1:4">
+      <c r="A1589" s="1">
+        <v>1587</v>
+      </c>
+      <c r="B1589" s="2">
+        <v>46149</v>
+      </c>
+      <c r="C1589">
+        <v>1</v>
+      </c>
+      <c r="D1589">
+        <v>463.41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1589"/>
+  <dimension ref="A1:D1590"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22630,6 +22630,20 @@
         <v>463.41</v>
       </c>
     </row>
+    <row r="1590" spans="1:4">
+      <c r="A1590" s="1">
+        <v>1588</v>
+      </c>
+      <c r="B1590" s="2">
+        <v>46150</v>
+      </c>
+      <c r="C1590">
+        <v>1</v>
+      </c>
+      <c r="D1590">
+        <v>463.41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1590"/>
+  <dimension ref="A1:D1591"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22644,6 +22644,20 @@
         <v>463.41</v>
       </c>
     </row>
+    <row r="1591" spans="1:4">
+      <c r="A1591" s="1">
+        <v>1589</v>
+      </c>
+      <c r="B1591" s="2">
+        <v>46151</v>
+      </c>
+      <c r="C1591">
+        <v>1</v>
+      </c>
+      <c r="D1591">
+        <v>461.26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1591"/>
+  <dimension ref="A1:D1592"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22658,6 +22658,20 @@
         <v>461.26</v>
       </c>
     </row>
+    <row r="1592" spans="1:4">
+      <c r="A1592" s="1">
+        <v>1590</v>
+      </c>
+      <c r="B1592" s="2">
+        <v>46152</v>
+      </c>
+      <c r="C1592">
+        <v>1</v>
+      </c>
+      <c r="D1592">
+        <v>461.26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1592"/>
+  <dimension ref="A1:D1594"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22672,6 +22672,34 @@
         <v>461.26</v>
       </c>
     </row>
+    <row r="1593" spans="1:4">
+      <c r="A1593" s="1">
+        <v>1591</v>
+      </c>
+      <c r="B1593" s="2">
+        <v>46153</v>
+      </c>
+      <c r="C1593">
+        <v>1</v>
+      </c>
+      <c r="D1593">
+        <v>461.26</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:4">
+      <c r="A1594" s="1">
+        <v>1592</v>
+      </c>
+      <c r="B1594" s="2">
+        <v>46154</v>
+      </c>
+      <c r="C1594">
+        <v>1</v>
+      </c>
+      <c r="D1594">
+        <v>461.26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1594"/>
+  <dimension ref="A1:D1595"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22700,6 +22700,20 @@
         <v>461.26</v>
       </c>
     </row>
+    <row r="1595" spans="1:4">
+      <c r="A1595" s="1">
+        <v>1593</v>
+      </c>
+      <c r="B1595" s="2">
+        <v>46155</v>
+      </c>
+      <c r="C1595">
+        <v>1</v>
+      </c>
+      <c r="D1595">
+        <v>463.91</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1595"/>
+  <dimension ref="A1:D1596"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22714,6 +22714,20 @@
         <v>463.91</v>
       </c>
     </row>
+    <row r="1596" spans="1:4">
+      <c r="A1596" s="1">
+        <v>1594</v>
+      </c>
+      <c r="B1596" s="2">
+        <v>46156</v>
+      </c>
+      <c r="C1596">
+        <v>1</v>
+      </c>
+      <c r="D1596">
+        <v>467.63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1596"/>
+  <dimension ref="A1:D1597"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22728,6 +22728,20 @@
         <v>467.63</v>
       </c>
     </row>
+    <row r="1597" spans="1:4">
+      <c r="A1597" s="1">
+        <v>1595</v>
+      </c>
+      <c r="B1597" s="2">
+        <v>46157</v>
+      </c>
+      <c r="C1597">
+        <v>1</v>
+      </c>
+      <c r="D1597">
+        <v>474.04</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1597"/>
+  <dimension ref="A1:D1598"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22742,6 +22742,20 @@
         <v>474.04</v>
       </c>
     </row>
+    <row r="1598" spans="1:4">
+      <c r="A1598" s="1">
+        <v>1596</v>
+      </c>
+      <c r="B1598" s="2">
+        <v>46158</v>
+      </c>
+      <c r="C1598">
+        <v>1</v>
+      </c>
+      <c r="D1598">
+        <v>470.17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1598"/>
+  <dimension ref="A1:D1600"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22756,6 +22756,34 @@
         <v>470.17</v>
       </c>
     </row>
+    <row r="1599" spans="1:4">
+      <c r="A1599" s="1">
+        <v>1597</v>
+      </c>
+      <c r="B1599" s="2">
+        <v>46159</v>
+      </c>
+      <c r="C1599">
+        <v>1</v>
+      </c>
+      <c r="D1599">
+        <v>470.17</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:4">
+      <c r="A1600" s="1">
+        <v>1598</v>
+      </c>
+      <c r="B1600" s="2">
+        <v>46160</v>
+      </c>
+      <c r="C1600">
+        <v>1</v>
+      </c>
+      <c r="D1600">
+        <v>470.17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1600"/>
+  <dimension ref="A1:D1601"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22784,6 +22784,20 @@
         <v>470.17</v>
       </c>
     </row>
+    <row r="1601" spans="1:4">
+      <c r="A1601" s="1">
+        <v>1599</v>
+      </c>
+      <c r="B1601" s="2">
+        <v>46161</v>
+      </c>
+      <c r="C1601">
+        <v>1</v>
+      </c>
+      <c r="D1601">
+        <v>467.58</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1601"/>
+  <dimension ref="A1:D1602"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22798,6 +22798,20 @@
         <v>467.58</v>
       </c>
     </row>
+    <row r="1602" spans="1:4">
+      <c r="A1602" s="1">
+        <v>1600</v>
+      </c>
+      <c r="B1602" s="2">
+        <v>46162</v>
+      </c>
+      <c r="C1602">
+        <v>1</v>
+      </c>
+      <c r="D1602">
+        <v>471.93</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1602"/>
+  <dimension ref="A1:D1603"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22812,6 +22812,20 @@
         <v>471.93</v>
       </c>
     </row>
+    <row r="1603" spans="1:4">
+      <c r="A1603" s="1">
+        <v>1601</v>
+      </c>
+      <c r="B1603" s="2">
+        <v>46163</v>
+      </c>
+      <c r="C1603">
+        <v>1</v>
+      </c>
+      <c r="D1603">
+        <v>471.77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1603"/>
+  <dimension ref="A1:D1604"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22826,6 +22826,20 @@
         <v>471.77</v>
       </c>
     </row>
+    <row r="1604" spans="1:4">
+      <c r="A1604" s="1">
+        <v>1602</v>
+      </c>
+      <c r="B1604" s="2">
+        <v>46164</v>
+      </c>
+      <c r="C1604">
+        <v>1</v>
+      </c>
+      <c r="D1604">
+        <v>471.45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1604"/>
+  <dimension ref="A1:D1605"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22840,6 +22840,20 @@
         <v>471.45</v>
       </c>
     </row>
+    <row r="1605" spans="1:4">
+      <c r="A1605" s="1">
+        <v>1603</v>
+      </c>
+      <c r="B1605" s="2">
+        <v>46165</v>
+      </c>
+      <c r="C1605">
+        <v>1</v>
+      </c>
+      <c r="D1605">
+        <v>470.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1605"/>
+  <dimension ref="A1:D1608"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22854,6 +22854,48 @@
         <v>470.8</v>
       </c>
     </row>
+    <row r="1606" spans="1:4">
+      <c r="A1606" s="1">
+        <v>1604</v>
+      </c>
+      <c r="B1606" s="2">
+        <v>46166</v>
+      </c>
+      <c r="C1606">
+        <v>1</v>
+      </c>
+      <c r="D1606">
+        <v>470.8</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:4">
+      <c r="A1607" s="1">
+        <v>1605</v>
+      </c>
+      <c r="B1607" s="2">
+        <v>46167</v>
+      </c>
+      <c r="C1607">
+        <v>1</v>
+      </c>
+      <c r="D1607">
+        <v>470.8</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:4">
+      <c r="A1608" s="1">
+        <v>1606</v>
+      </c>
+      <c r="B1608" s="2">
+        <v>46168</v>
+      </c>
+      <c r="C1608">
+        <v>1</v>
+      </c>
+      <c r="D1608">
+        <v>472.48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1608"/>
+  <dimension ref="A1:D1609"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22896,6 +22896,20 @@
         <v>472.48</v>
       </c>
     </row>
+    <row r="1609" spans="1:4">
+      <c r="A1609" s="1">
+        <v>1607</v>
+      </c>
+      <c r="B1609" s="2">
+        <v>46169</v>
+      </c>
+      <c r="C1609">
+        <v>1</v>
+      </c>
+      <c r="D1609">
+        <v>477.48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1609"/>
+  <dimension ref="A1:D1610"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22910,6 +22910,20 @@
         <v>477.48</v>
       </c>
     </row>
+    <row r="1610" spans="1:4">
+      <c r="A1610" s="1">
+        <v>1608</v>
+      </c>
+      <c r="B1610" s="2">
+        <v>46170</v>
+      </c>
+      <c r="C1610">
+        <v>1</v>
+      </c>
+      <c r="D1610">
+        <v>477.48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1610"/>
+  <dimension ref="A1:D1611"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22924,6 +22924,20 @@
         <v>477.48</v>
       </c>
     </row>
+    <row r="1611" spans="1:4">
+      <c r="A1611" s="1">
+        <v>1609</v>
+      </c>
+      <c r="B1611" s="2">
+        <v>46171</v>
+      </c>
+      <c r="C1611">
+        <v>1</v>
+      </c>
+      <c r="D1611">
+        <v>485.55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1611"/>
+  <dimension ref="A1:D1612"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22938,6 +22938,20 @@
         <v>485.55</v>
       </c>
     </row>
+    <row r="1612" spans="1:4">
+      <c r="A1612" s="1">
+        <v>1610</v>
+      </c>
+      <c r="B1612" s="2">
+        <v>46172</v>
+      </c>
+      <c r="C1612">
+        <v>1</v>
+      </c>
+      <c r="D1612">
+        <v>485.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1612"/>
+  <dimension ref="A1:D1613"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22952,6 +22952,20 @@
         <v>485.95</v>
       </c>
     </row>
+    <row r="1613" spans="1:4">
+      <c r="A1613" s="1">
+        <v>1611</v>
+      </c>
+      <c r="B1613" s="2">
+        <v>46173</v>
+      </c>
+      <c r="C1613">
+        <v>1</v>
+      </c>
+      <c r="D1613">
+        <v>485.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1613"/>
+  <dimension ref="A1:D1615"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22966,6 +22966,34 @@
         <v>485.95</v>
       </c>
     </row>
+    <row r="1614" spans="1:4">
+      <c r="A1614" s="1">
+        <v>1612</v>
+      </c>
+      <c r="B1614" s="2">
+        <v>46174</v>
+      </c>
+      <c r="C1614">
+        <v>1</v>
+      </c>
+      <c r="D1614">
+        <v>485.95</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:4">
+      <c r="A1615" s="1">
+        <v>1613</v>
+      </c>
+      <c r="B1615" s="2">
+        <v>46175</v>
+      </c>
+      <c r="C1615">
+        <v>1</v>
+      </c>
+      <c r="D1615">
+        <v>488.96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1615"/>
+  <dimension ref="A1:D1616"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22994,6 +22994,20 @@
         <v>488.96</v>
       </c>
     </row>
+    <row r="1616" spans="1:4">
+      <c r="A1616" s="1">
+        <v>1614</v>
+      </c>
+      <c r="B1616" s="2">
+        <v>46176</v>
+      </c>
+      <c r="C1616">
+        <v>1</v>
+      </c>
+      <c r="D1616">
+        <v>493.15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1616"/>
+  <dimension ref="A1:D1617"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23008,6 +23008,20 @@
         <v>493.15</v>
       </c>
     </row>
+    <row r="1617" spans="1:4">
+      <c r="A1617" s="1">
+        <v>1615</v>
+      </c>
+      <c r="B1617" s="2">
+        <v>46177</v>
+      </c>
+      <c r="C1617">
+        <v>1</v>
+      </c>
+      <c r="D1617">
+        <v>489.31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1617"/>
+  <dimension ref="A1:D1618"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23022,6 +23022,20 @@
         <v>489.31</v>
       </c>
     </row>
+    <row r="1618" spans="1:4">
+      <c r="A1618" s="1">
+        <v>1616</v>
+      </c>
+      <c r="B1618" s="2">
+        <v>46178</v>
+      </c>
+      <c r="C1618">
+        <v>1</v>
+      </c>
+      <c r="D1618">
+        <v>485.34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1618"/>
+  <dimension ref="A1:D1619"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23036,6 +23036,20 @@
         <v>485.34</v>
       </c>
     </row>
+    <row r="1619" spans="1:4">
+      <c r="A1619" s="1">
+        <v>1617</v>
+      </c>
+      <c r="B1619" s="2">
+        <v>46179</v>
+      </c>
+      <c r="C1619">
+        <v>1</v>
+      </c>
+      <c r="D1619">
+        <v>487.44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1619"/>
+  <dimension ref="A1:D1623"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23050,6 +23050,62 @@
         <v>487.44</v>
       </c>
     </row>
+    <row r="1620" spans="1:4">
+      <c r="A1620" s="1">
+        <v>1618</v>
+      </c>
+      <c r="B1620" s="2">
+        <v>46180</v>
+      </c>
+      <c r="C1620">
+        <v>1</v>
+      </c>
+      <c r="D1620">
+        <v>487.44</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:4">
+      <c r="A1621" s="1">
+        <v>1619</v>
+      </c>
+      <c r="B1621" s="2">
+        <v>46181</v>
+      </c>
+      <c r="C1621">
+        <v>1</v>
+      </c>
+      <c r="D1621">
+        <v>487.44</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:4">
+      <c r="A1622" s="1">
+        <v>1620</v>
+      </c>
+      <c r="B1622" s="2">
+        <v>46182</v>
+      </c>
+      <c r="C1622">
+        <v>1</v>
+      </c>
+      <c r="D1622">
+        <v>484.78</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:4">
+      <c r="A1623" s="1">
+        <v>1621</v>
+      </c>
+      <c r="B1623" s="2">
+        <v>46183</v>
+      </c>
+      <c r="C1623">
+        <v>1</v>
+      </c>
+      <c r="D1623">
+        <v>490.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1623"/>
+  <dimension ref="A1:D1624"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23106,6 +23106,20 @@
         <v>490.21</v>
       </c>
     </row>
+    <row r="1624" spans="1:4">
+      <c r="A1624" s="1">
+        <v>1622</v>
+      </c>
+      <c r="B1624" s="2">
+        <v>46184</v>
+      </c>
+      <c r="C1624">
+        <v>1</v>
+      </c>
+      <c r="D1624">
+        <v>488.59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1624"/>
+  <dimension ref="A1:D1625"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23120,6 +23120,20 @@
         <v>488.59</v>
       </c>
     </row>
+    <row r="1625" spans="1:4">
+      <c r="A1625" s="1">
+        <v>1623</v>
+      </c>
+      <c r="B1625" s="2">
+        <v>46185</v>
+      </c>
+      <c r="C1625">
+        <v>1</v>
+      </c>
+      <c r="D1625">
+        <v>487.76</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1625"/>
+  <dimension ref="A1:D1627"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23134,6 +23134,34 @@
         <v>487.76</v>
       </c>
     </row>
+    <row r="1626" spans="1:4">
+      <c r="A1626" s="1">
+        <v>1624</v>
+      </c>
+      <c r="B1626" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C1626">
+        <v>1</v>
+      </c>
+      <c r="D1626">
+        <v>489.33</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:4">
+      <c r="A1627" s="1">
+        <v>1625</v>
+      </c>
+      <c r="B1627" s="2">
+        <v>46187</v>
+      </c>
+      <c r="C1627">
+        <v>1</v>
+      </c>
+      <c r="D1627">
+        <v>489.33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1627"/>
+  <dimension ref="A1:D1629"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23162,6 +23162,34 @@
         <v>489.33</v>
       </c>
     </row>
+    <row r="1628" spans="1:4">
+      <c r="A1628" s="1">
+        <v>1626</v>
+      </c>
+      <c r="B1628" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C1628">
+        <v>1</v>
+      </c>
+      <c r="D1628">
+        <v>489.33</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:4">
+      <c r="A1629" s="1">
+        <v>1627</v>
+      </c>
+      <c r="B1629" s="2">
+        <v>46189</v>
+      </c>
+      <c r="C1629">
+        <v>1</v>
+      </c>
+      <c r="D1629">
+        <v>491.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1629"/>
+  <dimension ref="A1:D1630"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23190,6 +23190,20 @@
         <v>491.37</v>
       </c>
     </row>
+    <row r="1630" spans="1:4">
+      <c r="A1630" s="1">
+        <v>1628</v>
+      </c>
+      <c r="B1630" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C1630">
+        <v>1</v>
+      </c>
+      <c r="D1630">
+        <v>487.17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1630"/>
+  <dimension ref="A1:D1631"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23204,6 +23204,20 @@
         <v>487.17</v>
       </c>
     </row>
+    <row r="1631" spans="1:4">
+      <c r="A1631" s="1">
+        <v>1629</v>
+      </c>
+      <c r="B1631" s="2">
+        <v>46191</v>
+      </c>
+      <c r="C1631">
+        <v>1</v>
+      </c>
+      <c r="D1631">
+        <v>489.39</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1631"/>
+  <dimension ref="A1:D1632"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23218,6 +23218,20 @@
         <v>489.39</v>
       </c>
     </row>
+    <row r="1632" spans="1:4">
+      <c r="A1632" s="1">
+        <v>1630</v>
+      </c>
+      <c r="B1632" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C1632">
+        <v>1</v>
+      </c>
+      <c r="D1632">
+        <v>487.73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1632"/>
+  <dimension ref="A1:D1633"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23232,6 +23232,20 @@
         <v>487.73</v>
       </c>
     </row>
+    <row r="1633" spans="1:4">
+      <c r="A1633" s="1">
+        <v>1631</v>
+      </c>
+      <c r="B1633" s="2">
+        <v>46193</v>
+      </c>
+      <c r="C1633">
+        <v>1</v>
+      </c>
+      <c r="D1633">
+        <v>488.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1633"/>
+  <dimension ref="A1:D1636"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23246,6 +23246,48 @@
         <v>488.37</v>
       </c>
     </row>
+    <row r="1634" spans="1:4">
+      <c r="A1634" s="1">
+        <v>1632</v>
+      </c>
+      <c r="B1634" s="2">
+        <v>46194</v>
+      </c>
+      <c r="C1634">
+        <v>1</v>
+      </c>
+      <c r="D1634">
+        <v>488.37</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:4">
+      <c r="A1635" s="1">
+        <v>1633</v>
+      </c>
+      <c r="B1635" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C1635">
+        <v>1</v>
+      </c>
+      <c r="D1635">
+        <v>488.37</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:4">
+      <c r="A1636" s="1">
+        <v>1634</v>
+      </c>
+      <c r="B1636" s="2">
+        <v>46196</v>
+      </c>
+      <c r="C1636">
+        <v>1</v>
+      </c>
+      <c r="D1636">
+        <v>487.01</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1636"/>
+  <dimension ref="A1:D1637"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23288,6 +23288,20 @@
         <v>487.01</v>
       </c>
     </row>
+    <row r="1637" spans="1:4">
+      <c r="A1637" s="1">
+        <v>1635</v>
+      </c>
+      <c r="B1637" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C1637">
+        <v>1</v>
+      </c>
+      <c r="D1637">
+        <v>486.19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1637"/>
+  <dimension ref="A1:D1638"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23302,6 +23302,20 @@
         <v>486.19</v>
       </c>
     </row>
+    <row r="1638" spans="1:4">
+      <c r="A1638" s="1">
+        <v>1636</v>
+      </c>
+      <c r="B1638" s="2">
+        <v>46198</v>
+      </c>
+      <c r="C1638">
+        <v>1</v>
+      </c>
+      <c r="D1638">
+        <v>487.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1638"/>
+  <dimension ref="A1:D1639"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23316,6 +23316,20 @@
         <v>487.02</v>
       </c>
     </row>
+    <row r="1639" spans="1:4">
+      <c r="A1639" s="1">
+        <v>1637</v>
+      </c>
+      <c r="B1639" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C1639">
+        <v>1</v>
+      </c>
+      <c r="D1639">
+        <v>485.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1639"/>
+  <dimension ref="A1:D1640"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23330,6 +23330,20 @@
         <v>485.4</v>
       </c>
     </row>
+    <row r="1640" spans="1:4">
+      <c r="A1640" s="1">
+        <v>1638</v>
+      </c>
+      <c r="B1640" s="2">
+        <v>46200</v>
+      </c>
+      <c r="C1640">
+        <v>1</v>
+      </c>
+      <c r="D1640">
+        <v>486.47</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1640"/>
+  <dimension ref="A1:D1643"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23344,6 +23344,48 @@
         <v>486.47</v>
       </c>
     </row>
+    <row r="1641" spans="1:4">
+      <c r="A1641" s="1">
+        <v>1639</v>
+      </c>
+      <c r="B1641" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C1641">
+        <v>1</v>
+      </c>
+      <c r="D1641">
+        <v>486.47</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:4">
+      <c r="A1642" s="1">
+        <v>1640</v>
+      </c>
+      <c r="B1642" s="2">
+        <v>46202</v>
+      </c>
+      <c r="C1642">
+        <v>1</v>
+      </c>
+      <c r="D1642">
+        <v>486.47</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:4">
+      <c r="A1643" s="1">
+        <v>1641</v>
+      </c>
+      <c r="B1643" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C1643">
+        <v>1</v>
+      </c>
+      <c r="D1643">
+        <v>485.82</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1643"/>
+  <dimension ref="A1:D1644"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23386,6 +23386,20 @@
         <v>485.82</v>
       </c>
     </row>
+    <row r="1644" spans="1:4">
+      <c r="A1644" s="1">
+        <v>1642</v>
+      </c>
+      <c r="B1644" s="2">
+        <v>46204</v>
+      </c>
+      <c r="C1644">
+        <v>1</v>
+      </c>
+      <c r="D1644">
+        <v>480.72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1644"/>
+  <dimension ref="A1:D1645"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23400,6 +23400,20 @@
         <v>480.72</v>
       </c>
     </row>
+    <row r="1645" spans="1:4">
+      <c r="A1645" s="1">
+        <v>1643</v>
+      </c>
+      <c r="B1645" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C1645">
+        <v>1</v>
+      </c>
+      <c r="D1645">
+        <v>479.26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1645"/>
+  <dimension ref="A1:D1646"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23414,6 +23414,20 @@
         <v>479.26</v>
       </c>
     </row>
+    <row r="1646" spans="1:4">
+      <c r="A1646" s="1">
+        <v>1644</v>
+      </c>
+      <c r="B1646" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C1646">
+        <v>1</v>
+      </c>
+      <c r="D1646">
+        <v>474.47</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1646"/>
+  <dimension ref="A1:D1647"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23428,6 +23428,20 @@
         <v>474.47</v>
       </c>
     </row>
+    <row r="1647" spans="1:4">
+      <c r="A1647" s="1">
+        <v>1645</v>
+      </c>
+      <c r="B1647" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C1647">
+        <v>1</v>
+      </c>
+      <c r="D1647">
+        <v>472.03</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1647"/>
+  <dimension ref="A1:D1650"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23442,6 +23442,48 @@
         <v>472.03</v>
       </c>
     </row>
+    <row r="1648" spans="1:4">
+      <c r="A1648" s="1">
+        <v>1646</v>
+      </c>
+      <c r="B1648" s="2">
+        <v>46208</v>
+      </c>
+      <c r="C1648">
+        <v>1</v>
+      </c>
+      <c r="D1648">
+        <v>472.03</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:4">
+      <c r="A1649" s="1">
+        <v>1647</v>
+      </c>
+      <c r="B1649" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C1649">
+        <v>1</v>
+      </c>
+      <c r="D1649">
+        <v>472.03</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:4">
+      <c r="A1650" s="1">
+        <v>1648</v>
+      </c>
+      <c r="B1650" s="2">
+        <v>46210</v>
+      </c>
+      <c r="C1650">
+        <v>1</v>
+      </c>
+      <c r="D1650">
+        <v>472.03</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1650"/>
+  <dimension ref="A1:D1651"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23484,6 +23484,20 @@
         <v>472.03</v>
       </c>
     </row>
+    <row r="1651" spans="1:4">
+      <c r="A1651" s="1">
+        <v>1649</v>
+      </c>
+      <c r="B1651" s="2">
+        <v>46211</v>
+      </c>
+      <c r="C1651">
+        <v>1</v>
+      </c>
+      <c r="D1651">
+        <v>471.04</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1651"/>
+  <dimension ref="A1:D1652"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23498,6 +23498,20 @@
         <v>471.04</v>
       </c>
     </row>
+    <row r="1652" spans="1:4">
+      <c r="A1652" s="1">
+        <v>1650</v>
+      </c>
+      <c r="B1652" s="2">
+        <v>46212</v>
+      </c>
+      <c r="C1652">
+        <v>1</v>
+      </c>
+      <c r="D1652">
+        <v>467.98</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1652"/>
+  <dimension ref="A1:D1653"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23512,6 +23512,20 @@
         <v>467.98</v>
       </c>
     </row>
+    <row r="1653" spans="1:4">
+      <c r="A1653" s="1">
+        <v>1651</v>
+      </c>
+      <c r="B1653" s="2">
+        <v>46213</v>
+      </c>
+      <c r="C1653">
+        <v>1</v>
+      </c>
+      <c r="D1653">
+        <v>467.41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1653"/>
+  <dimension ref="A1:D1654"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23526,6 +23526,20 @@
         <v>467.41</v>
       </c>
     </row>
+    <row r="1654" spans="1:4">
+      <c r="A1654" s="1">
+        <v>1652</v>
+      </c>
+      <c r="B1654" s="2">
+        <v>46214</v>
+      </c>
+      <c r="C1654">
+        <v>1</v>
+      </c>
+      <c r="D1654">
+        <v>464.71</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1654"/>
+  <dimension ref="A1:D1657"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23540,6 +23540,48 @@
         <v>464.71</v>
       </c>
     </row>
+    <row r="1655" spans="1:4">
+      <c r="A1655" s="1">
+        <v>1653</v>
+      </c>
+      <c r="B1655" s="2">
+        <v>46215</v>
+      </c>
+      <c r="C1655">
+        <v>1</v>
+      </c>
+      <c r="D1655">
+        <v>464.71</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:4">
+      <c r="A1656" s="1">
+        <v>1654</v>
+      </c>
+      <c r="B1656" s="2">
+        <v>46216</v>
+      </c>
+      <c r="C1656">
+        <v>1</v>
+      </c>
+      <c r="D1656">
+        <v>464.71</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:4">
+      <c r="A1657" s="1">
+        <v>1655</v>
+      </c>
+      <c r="B1657" s="2">
+        <v>46217</v>
+      </c>
+      <c r="C1657">
+        <v>1</v>
+      </c>
+      <c r="D1657">
+        <v>477.11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1657"/>
+  <dimension ref="A1:D1658"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23582,6 +23582,20 @@
         <v>477.11</v>
       </c>
     </row>
+    <row r="1658" spans="1:4">
+      <c r="A1658" s="1">
+        <v>1656</v>
+      </c>
+      <c r="B1658" s="2">
+        <v>46218</v>
+      </c>
+      <c r="C1658">
+        <v>1</v>
+      </c>
+      <c r="D1658">
+        <v>468.88</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1658"/>
+  <dimension ref="A1:D1659"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23596,6 +23596,20 @@
         <v>468.88</v>
       </c>
     </row>
+    <row r="1659" spans="1:4">
+      <c r="A1659" s="1">
+        <v>1657</v>
+      </c>
+      <c r="B1659" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C1659">
+        <v>1</v>
+      </c>
+      <c r="D1659">
+        <v>469.71</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1659"/>
+  <dimension ref="A1:D1660"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23610,6 +23610,20 @@
         <v>469.71</v>
       </c>
     </row>
+    <row r="1660" spans="1:4">
+      <c r="A1660" s="1">
+        <v>1658</v>
+      </c>
+      <c r="B1660" s="2">
+        <v>46220</v>
+      </c>
+      <c r="C1660">
+        <v>1</v>
+      </c>
+      <c r="D1660">
+        <v>472.34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1660"/>
+  <dimension ref="A1:D1661"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23624,6 +23624,20 @@
         <v>472.34</v>
       </c>
     </row>
+    <row r="1661" spans="1:4">
+      <c r="A1661" s="1">
+        <v>1659</v>
+      </c>
+      <c r="B1661" s="2">
+        <v>46221</v>
+      </c>
+      <c r="C1661">
+        <v>1</v>
+      </c>
+      <c r="D1661">
+        <v>469.83</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1661"/>
+  <dimension ref="A1:D1663"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23638,6 +23638,34 @@
         <v>469.83</v>
       </c>
     </row>
+    <row r="1662" spans="1:4">
+      <c r="A1662" s="1">
+        <v>1660</v>
+      </c>
+      <c r="B1662" s="2">
+        <v>46222</v>
+      </c>
+      <c r="C1662">
+        <v>1</v>
+      </c>
+      <c r="D1662">
+        <v>469.83</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:4">
+      <c r="A1663" s="1">
+        <v>1661</v>
+      </c>
+      <c r="B1663" s="2">
+        <v>46223</v>
+      </c>
+      <c r="C1663">
+        <v>1</v>
+      </c>
+      <c r="D1663">
+        <v>469.83</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1663"/>
+  <dimension ref="A1:D1664"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23666,6 +23666,20 @@
         <v>469.83</v>
       </c>
     </row>
+    <row r="1664" spans="1:4">
+      <c r="A1664" s="1">
+        <v>1662</v>
+      </c>
+      <c r="B1664" s="2">
+        <v>46224</v>
+      </c>
+      <c r="C1664">
+        <v>1</v>
+      </c>
+      <c r="D1664">
+        <v>470.28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1664"/>
+  <dimension ref="A1:D1665"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23680,6 +23680,20 @@
         <v>470.28</v>
       </c>
     </row>
+    <row r="1665" spans="1:4">
+      <c r="A1665" s="1">
+        <v>1663</v>
+      </c>
+      <c r="B1665" s="2">
+        <v>46225</v>
+      </c>
+      <c r="C1665">
+        <v>1</v>
+      </c>
+      <c r="D1665">
+        <v>469.59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1665"/>
+  <dimension ref="A1:D1666"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23694,6 +23694,20 @@
         <v>469.59</v>
       </c>
     </row>
+    <row r="1666" spans="1:4">
+      <c r="A1666" s="1">
+        <v>1664</v>
+      </c>
+      <c r="B1666" s="2">
+        <v>46226</v>
+      </c>
+      <c r="C1666">
+        <v>1</v>
+      </c>
+      <c r="D1666">
+        <v>467.65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1666"/>
+  <dimension ref="A1:D1667"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23708,6 +23708,20 @@
         <v>467.65</v>
       </c>
     </row>
+    <row r="1667" spans="1:4">
+      <c r="A1667" s="1">
+        <v>1665</v>
+      </c>
+      <c r="B1667" s="2">
+        <v>46227</v>
+      </c>
+      <c r="C1667">
+        <v>1</v>
+      </c>
+      <c r="D1667">
+        <v>465.74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1667"/>
+  <dimension ref="A1:D1668"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23722,6 +23722,20 @@
         <v>465.74</v>
       </c>
     </row>
+    <row r="1668" spans="1:4">
+      <c r="A1668" s="1">
+        <v>1666</v>
+      </c>
+      <c r="B1668" s="2">
+        <v>46228</v>
+      </c>
+      <c r="C1668">
+        <v>1</v>
+      </c>
+      <c r="D1668">
+        <v>476.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1668"/>
+  <dimension ref="A1:D1671"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23736,6 +23736,48 @@
         <v>476.07</v>
       </c>
     </row>
+    <row r="1669" spans="1:4">
+      <c r="A1669" s="1">
+        <v>1667</v>
+      </c>
+      <c r="B1669" s="2">
+        <v>46229</v>
+      </c>
+      <c r="C1669">
+        <v>1</v>
+      </c>
+      <c r="D1669">
+        <v>476.07</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:4">
+      <c r="A1670" s="1">
+        <v>1668</v>
+      </c>
+      <c r="B1670" s="2">
+        <v>46230</v>
+      </c>
+      <c r="C1670">
+        <v>1</v>
+      </c>
+      <c r="D1670">
+        <v>476.07</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:4">
+      <c r="A1671" s="1">
+        <v>1669</v>
+      </c>
+      <c r="B1671" s="2">
+        <v>46231</v>
+      </c>
+      <c r="C1671">
+        <v>1</v>
+      </c>
+      <c r="D1671">
+        <v>473.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1671"/>
+  <dimension ref="A1:D1672"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23778,6 +23778,20 @@
         <v>473.4</v>
       </c>
     </row>
+    <row r="1672" spans="1:4">
+      <c r="A1672" s="1">
+        <v>1670</v>
+      </c>
+      <c r="B1672" s="2">
+        <v>46232</v>
+      </c>
+      <c r="C1672">
+        <v>1</v>
+      </c>
+      <c r="D1672">
+        <v>476.75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1672"/>
+  <dimension ref="A1:D1673"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23792,6 +23792,20 @@
         <v>476.75</v>
       </c>
     </row>
+    <row r="1673" spans="1:4">
+      <c r="A1673" s="1">
+        <v>1671</v>
+      </c>
+      <c r="B1673" s="2">
+        <v>46233</v>
+      </c>
+      <c r="C1673">
+        <v>1</v>
+      </c>
+      <c r="D1673">
+        <v>477.17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1673"/>
+  <dimension ref="A1:D1674"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23806,6 +23806,20 @@
         <v>477.17</v>
       </c>
     </row>
+    <row r="1674" spans="1:4">
+      <c r="A1674" s="1">
+        <v>1672</v>
+      </c>
+      <c r="B1674" s="2">
+        <v>46234</v>
+      </c>
+      <c r="C1674">
+        <v>1</v>
+      </c>
+      <c r="D1674">
+        <v>474.63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1674"/>
+  <dimension ref="A1:D1675"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23820,6 +23820,20 @@
         <v>474.63</v>
       </c>
     </row>
+    <row r="1675" spans="1:4">
+      <c r="A1675" s="1">
+        <v>1673</v>
+      </c>
+      <c r="B1675" s="2">
+        <v>46235</v>
+      </c>
+      <c r="C1675">
+        <v>1</v>
+      </c>
+      <c r="D1675">
+        <v>473.59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1675"/>
+  <dimension ref="A1:D1678"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23834,6 +23834,48 @@
         <v>473.59</v>
       </c>
     </row>
+    <row r="1676" spans="1:4">
+      <c r="A1676" s="1">
+        <v>1674</v>
+      </c>
+      <c r="B1676" s="2">
+        <v>46236</v>
+      </c>
+      <c r="C1676">
+        <v>1</v>
+      </c>
+      <c r="D1676">
+        <v>473.59</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:4">
+      <c r="A1677" s="1">
+        <v>1675</v>
+      </c>
+      <c r="B1677" s="2">
+        <v>46237</v>
+      </c>
+      <c r="C1677">
+        <v>1</v>
+      </c>
+      <c r="D1677">
+        <v>473.59</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:4">
+      <c r="A1678" s="1">
+        <v>1676</v>
+      </c>
+      <c r="B1678" s="2">
+        <v>46238</v>
+      </c>
+      <c r="C1678">
+        <v>1</v>
+      </c>
+      <c r="D1678">
+        <v>475.38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1678"/>
+  <dimension ref="A1:D1679"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23876,6 +23876,20 @@
         <v>475.38</v>
       </c>
     </row>
+    <row r="1679" spans="1:4">
+      <c r="A1679" s="1">
+        <v>1677</v>
+      </c>
+      <c r="B1679" s="2">
+        <v>46239</v>
+      </c>
+      <c r="C1679">
+        <v>1</v>
+      </c>
+      <c r="D1679">
+        <v>471.98</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1679"/>
+  <dimension ref="A1:D1680"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23890,6 +23890,20 @@
         <v>471.98</v>
       </c>
     </row>
+    <row r="1680" spans="1:4">
+      <c r="A1680" s="1">
+        <v>1678</v>
+      </c>
+      <c r="B1680" s="2">
+        <v>46240</v>
+      </c>
+      <c r="C1680">
+        <v>1</v>
+      </c>
+      <c r="D1680">
+        <v>469.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1680"/>
+  <dimension ref="A1:D1681"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23904,6 +23904,20 @@
         <v>469.85</v>
       </c>
     </row>
+    <row r="1681" spans="1:4">
+      <c r="A1681" s="1">
+        <v>1679</v>
+      </c>
+      <c r="B1681" s="2">
+        <v>46241</v>
+      </c>
+      <c r="C1681">
+        <v>1</v>
+      </c>
+      <c r="D1681">
+        <v>467.48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1681"/>
+  <dimension ref="A1:D1682"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23918,6 +23918,20 @@
         <v>467.48</v>
       </c>
     </row>
+    <row r="1682" spans="1:4">
+      <c r="A1682" s="1">
+        <v>1680</v>
+      </c>
+      <c r="B1682" s="2">
+        <v>46242</v>
+      </c>
+      <c r="C1682">
+        <v>1</v>
+      </c>
+      <c r="D1682">
+        <v>469.93</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1682"/>
+  <dimension ref="A1:D1683"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23932,6 +23932,20 @@
         <v>469.93</v>
       </c>
     </row>
+    <row r="1683" spans="1:4">
+      <c r="A1683" s="1">
+        <v>1681</v>
+      </c>
+      <c r="B1683" s="2">
+        <v>46243</v>
+      </c>
+      <c r="C1683">
+        <v>1</v>
+      </c>
+      <c r="D1683">
+        <v>469.93</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1683"/>
+  <dimension ref="A1:D1685"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23946,6 +23946,34 @@
         <v>469.93</v>
       </c>
     </row>
+    <row r="1684" spans="1:4">
+      <c r="A1684" s="1">
+        <v>1682</v>
+      </c>
+      <c r="B1684" s="2">
+        <v>46244</v>
+      </c>
+      <c r="C1684">
+        <v>1</v>
+      </c>
+      <c r="D1684">
+        <v>469.93</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:4">
+      <c r="A1685" s="1">
+        <v>1683</v>
+      </c>
+      <c r="B1685" s="2">
+        <v>46245</v>
+      </c>
+      <c r="C1685">
+        <v>1</v>
+      </c>
+      <c r="D1685">
+        <v>466.08</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1685"/>
+  <dimension ref="A1:D1686"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23974,6 +23974,20 @@
         <v>466.08</v>
       </c>
     </row>
+    <row r="1686" spans="1:4">
+      <c r="A1686" s="1">
+        <v>1684</v>
+      </c>
+      <c r="B1686" s="2">
+        <v>46246</v>
+      </c>
+      <c r="C1686">
+        <v>1</v>
+      </c>
+      <c r="D1686">
+        <v>465.74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1686"/>
+  <dimension ref="A1:D1687"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23988,6 +23988,20 @@
         <v>465.74</v>
       </c>
     </row>
+    <row r="1687" spans="1:4">
+      <c r="A1687" s="1">
+        <v>1685</v>
+      </c>
+      <c r="B1687" s="2">
+        <v>46247</v>
+      </c>
+      <c r="C1687">
+        <v>1</v>
+      </c>
+      <c r="D1687">
+        <v>465.19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1687"/>
+  <dimension ref="A1:D1688"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24002,6 +24002,20 @@
         <v>465.19</v>
       </c>
     </row>
+    <row r="1688" spans="1:4">
+      <c r="A1688" s="1">
+        <v>1686</v>
+      </c>
+      <c r="B1688" s="2">
+        <v>46248</v>
+      </c>
+      <c r="C1688">
+        <v>1</v>
+      </c>
+      <c r="D1688">
+        <v>465.08</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1688"/>
+  <dimension ref="A1:D1686"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23979,41 +23979,13 @@
         <v>1684</v>
       </c>
       <c r="B1686" s="2">
-        <v>46246</v>
+        <v>46249</v>
       </c>
       <c r="C1686">
         <v>1</v>
       </c>
       <c r="D1686">
-        <v>465.74</v>
-      </c>
-    </row>
-    <row r="1687" spans="1:4">
-      <c r="A1687" s="1">
-        <v>1685</v>
-      </c>
-      <c r="B1687" s="2">
-        <v>46247</v>
-      </c>
-      <c r="C1687">
-        <v>1</v>
-      </c>
-      <c r="D1687">
-        <v>465.19</v>
-      </c>
-    </row>
-    <row r="1688" spans="1:4">
-      <c r="A1688" s="1">
-        <v>1686</v>
-      </c>
-      <c r="B1688" s="2">
-        <v>46248</v>
-      </c>
-      <c r="C1688">
-        <v>1</v>
-      </c>
-      <c r="D1688">
-        <v>465.08</v>
+        <v>464.02</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1686"/>
+  <dimension ref="A1:D1691"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23979,13 +23979,83 @@
         <v>1684</v>
       </c>
       <c r="B1686" s="2">
+        <v>46246</v>
+      </c>
+      <c r="C1686">
+        <v>1</v>
+      </c>
+      <c r="D1686">
+        <v>465.74</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:4">
+      <c r="A1687" s="1">
+        <v>1685</v>
+      </c>
+      <c r="B1687" s="2">
+        <v>46247</v>
+      </c>
+      <c r="C1687">
+        <v>1</v>
+      </c>
+      <c r="D1687">
+        <v>465.19</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:4">
+      <c r="A1688" s="1">
+        <v>1686</v>
+      </c>
+      <c r="B1688" s="2">
+        <v>46248</v>
+      </c>
+      <c r="C1688">
+        <v>1</v>
+      </c>
+      <c r="D1688">
+        <v>465.08</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:4">
+      <c r="A1689" s="1">
+        <v>1687</v>
+      </c>
+      <c r="B1689" s="2">
         <v>46249</v>
       </c>
-      <c r="C1686">
-        <v>1</v>
-      </c>
-      <c r="D1686">
+      <c r="C1689">
+        <v>1</v>
+      </c>
+      <c r="D1689">
         <v>464.02</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:4">
+      <c r="A1690" s="1">
+        <v>1688</v>
+      </c>
+      <c r="B1690" s="2">
+        <v>46251</v>
+      </c>
+      <c r="C1690">
+        <v>1</v>
+      </c>
+      <c r="D1690">
+        <v>464.02</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:4">
+      <c r="A1691" s="1">
+        <v>1689</v>
+      </c>
+      <c r="B1691" s="2">
+        <v>46252</v>
+      </c>
+      <c r="C1691">
+        <v>1</v>
+      </c>
+      <c r="D1691">
+        <v>461.39</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1691"/>
+  <dimension ref="A1:D1692"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24058,6 +24058,20 @@
         <v>461.39</v>
       </c>
     </row>
+    <row r="1692" spans="1:4">
+      <c r="A1692" s="1">
+        <v>1690</v>
+      </c>
+      <c r="B1692" s="2">
+        <v>46253</v>
+      </c>
+      <c r="C1692">
+        <v>1</v>
+      </c>
+      <c r="D1692">
+        <v>460.13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -24063,13 +24063,13 @@
         <v>1690</v>
       </c>
       <c r="B1692" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C1692">
         <v>1</v>
       </c>
       <c r="D1692">
-        <v>460.13</v>
+        <v>462.22</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1663"/>
+  <dimension ref="A1:D1664"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23666,6 +23666,20 @@
         <v>458.23</v>
       </c>
     </row>
+    <row r="1664" spans="1:4">
+      <c r="A1664" s="1">
+        <v>1662</v>
+      </c>
+      <c r="B1664" s="2">
+        <v>46256</v>
+      </c>
+      <c r="C1664">
+        <v>1</v>
+      </c>
+      <c r="D1664">
+        <v>456.88</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1664"/>
+  <dimension ref="A1:D1667"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23680,6 +23680,48 @@
         <v>456.88</v>
       </c>
     </row>
+    <row r="1665" spans="1:4">
+      <c r="A1665" s="1">
+        <v>1663</v>
+      </c>
+      <c r="B1665" s="2">
+        <v>46257</v>
+      </c>
+      <c r="C1665">
+        <v>1</v>
+      </c>
+      <c r="D1665">
+        <v>456.88</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:4">
+      <c r="A1666" s="1">
+        <v>1664</v>
+      </c>
+      <c r="B1666" s="2">
+        <v>46258</v>
+      </c>
+      <c r="C1666">
+        <v>1</v>
+      </c>
+      <c r="D1666">
+        <v>456.88</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:4">
+      <c r="A1667" s="1">
+        <v>1665</v>
+      </c>
+      <c r="B1667" s="2">
+        <v>46259</v>
+      </c>
+      <c r="C1667">
+        <v>1</v>
+      </c>
+      <c r="D1667">
+        <v>457.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1667"/>
+  <dimension ref="A1:D1668"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23722,6 +23722,20 @@
         <v>457.99</v>
       </c>
     </row>
+    <row r="1668" spans="1:4">
+      <c r="A1668" s="1">
+        <v>1666</v>
+      </c>
+      <c r="B1668" s="2">
+        <v>46260</v>
+      </c>
+      <c r="C1668">
+        <v>1</v>
+      </c>
+      <c r="D1668">
+        <v>458.48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1668"/>
+  <dimension ref="A1:D1669"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23736,6 +23736,20 @@
         <v>458.48</v>
       </c>
     </row>
+    <row r="1669" spans="1:4">
+      <c r="A1669" s="1">
+        <v>1667</v>
+      </c>
+      <c r="B1669" s="2">
+        <v>46261</v>
+      </c>
+      <c r="C1669">
+        <v>1</v>
+      </c>
+      <c r="D1669">
+        <v>458.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1669"/>
+  <dimension ref="A1:D1670"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23750,6 +23750,20 @@
         <v>458.87</v>
       </c>
     </row>
+    <row r="1670" spans="1:4">
+      <c r="A1670" s="1">
+        <v>1668</v>
+      </c>
+      <c r="B1670" s="2">
+        <v>46262</v>
+      </c>
+      <c r="C1670">
+        <v>1</v>
+      </c>
+      <c r="D1670">
+        <v>462.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1670"/>
+  <dimension ref="A1:D1671"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23764,6 +23764,20 @@
         <v>462.3</v>
       </c>
     </row>
+    <row r="1671" spans="1:4">
+      <c r="A1671" s="1">
+        <v>1669</v>
+      </c>
+      <c r="B1671" s="2">
+        <v>46263</v>
+      </c>
+      <c r="C1671">
+        <v>1</v>
+      </c>
+      <c r="D1671">
+        <v>464.77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1671"/>
+  <dimension ref="A1:D1674"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23778,6 +23778,48 @@
         <v>464.77</v>
       </c>
     </row>
+    <row r="1672" spans="1:4">
+      <c r="A1672" s="1">
+        <v>1670</v>
+      </c>
+      <c r="B1672" s="2">
+        <v>46264</v>
+      </c>
+      <c r="C1672">
+        <v>1</v>
+      </c>
+      <c r="D1672">
+        <v>464.77</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:4">
+      <c r="A1673" s="1">
+        <v>1671</v>
+      </c>
+      <c r="B1673" s="2">
+        <v>46265</v>
+      </c>
+      <c r="C1673">
+        <v>1</v>
+      </c>
+      <c r="D1673">
+        <v>464.77</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:4">
+      <c r="A1674" s="1">
+        <v>1672</v>
+      </c>
+      <c r="B1674" s="2">
+        <v>46266</v>
+      </c>
+      <c r="C1674">
+        <v>1</v>
+      </c>
+      <c r="D1674">
+        <v>462.31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/nbk_tenge.xlsx
+++ b/LME/parser_beta_2.0/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1674"/>
+  <dimension ref="A1:D1675"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23820,6 +23820,20 @@
         <v>462.31</v>
       </c>
     </row>
+    <row r="1675" spans="1:4">
+      <c r="A1675" s="1">
+        <v>1673</v>
+      </c>
+      <c r="B1675" s="2">
+        <v>46267</v>
+      </c>
+      <c r="C1675">
+        <v>1</v>
+      </c>
+      <c r="D1675">
+        <v>458.45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
